--- a/Testing.xlsx
+++ b/Testing.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahbub\Documents\GitHub\EnergyPLANDomainKnowledgeEAStep1\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="75" windowWidth="20055" windowHeight="7935"/>
   </bookViews>
@@ -11,12 +16,12 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="20">
   <si>
     <t>SinglePointCrossoverFavorMaximizationOfPP</t>
   </si>
@@ -81,8 +86,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -127,6 +132,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -173,7 +186,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -205,9 +218,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -239,6 +253,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -414,9 +429,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -424,7 +439,7 @@
     <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -441,7 +456,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -455,7 +470,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -469,12 +484,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -488,7 +503,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -498,11 +513,14 @@
       <c r="C6" t="s">
         <v>16</v>
       </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
       <c r="E6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -512,26 +530,29 @@
       <c r="C7" t="s">
         <v>16</v>
       </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
       <c r="E7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:5" s="2" customFormat="1">
+    <row r="12" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -545,7 +566,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -559,12 +580,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>10</v>
       </c>
@@ -574,11 +595,14 @@
       <c r="C16" t="s">
         <v>16</v>
       </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
       <c r="E16" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -588,11 +612,14 @@
       <c r="C17" t="s">
         <v>16</v>
       </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
       <c r="E17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -606,7 +633,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -617,18 +644,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
